--- a/optiV4/Resultats_Optimisation_PySR_LinearV2_annee_dyn.xlsx
+++ b/optiV4/Resultats_Optimisation_PySR_LinearV2_annee_dyn.xlsx
@@ -476,7 +476,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>4.552996576929043</v>
+        <v>4.552996576929042</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.04328126285486597</v>
+        <v>0.04328126285486596</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -524,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>-0.07052618599970853</v>
+        <v>-0.07052618599970857</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -540,7 +540,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>-0.04333480993134033</v>
+        <v>-0.04333480993134031</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -564,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>5.929503294895596</v>
+        <v>5.929503294895595</v>
       </c>
     </row>
   </sheetData>
@@ -3307,7 +3307,7 @@
         <v>20.25401142473306</v>
       </c>
       <c r="C8">
-        <v>1.49281712185403E-11</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -3316,7 +3316,7 @@
         <v>-0.00272</v>
       </c>
       <c r="F8">
-        <v>-1.015115642860741E-17</v>
+        <v>-0</v>
       </c>
       <c r="G8">
         <v>20</v>
@@ -3385,7 +3385,7 @@
         <v>21.26422119687038</v>
       </c>
       <c r="C11">
-        <v>8.781277187376647E-13</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -3394,7 +3394,7 @@
         <v>-0.00318</v>
       </c>
       <c r="F11">
-        <v>-6.981115363964435E-19</v>
+        <v>-0</v>
       </c>
       <c r="G11">
         <v>20</v>
@@ -3671,7 +3671,7 @@
         <v>24</v>
       </c>
       <c r="C22">
-        <v>2.634383156212994E-12</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3680,7 +3680,7 @@
         <v>-0.00465</v>
       </c>
       <c r="F22">
-        <v>-3.062470419097606E-18</v>
+        <v>-0</v>
       </c>
       <c r="G22">
         <v>20</v>
@@ -3775,7 +3775,7 @@
         <v>24</v>
       </c>
       <c r="C26">
-        <v>2.634383156212994E-12</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>-0.00329</v>
       </c>
       <c r="F26">
-        <v>-2.166780145985187E-18</v>
+        <v>-0</v>
       </c>
       <c r="G26">
         <v>20</v>
@@ -4321,7 +4321,7 @@
         <v>22.16267937632242</v>
       </c>
       <c r="C47">
-        <v>2.634383156212994E-12</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -4330,7 +4330,7 @@
         <v>-8.999999999999999E-05</v>
       </c>
       <c r="F47">
-        <v>-5.927362101479236E-20</v>
+        <v>-0</v>
       </c>
       <c r="G47">
         <v>20</v>
@@ -4425,7 +4425,7 @@
         <v>21.98362456826375</v>
       </c>
       <c r="C51">
-        <v>7.025021749901318E-12</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>-3E-05</v>
       </c>
       <c r="F51">
-        <v>-5.268766312425988E-20</v>
+        <v>-0</v>
       </c>
       <c r="G51">
         <v>20</v>
@@ -4503,7 +4503,7 @@
         <v>21.87079532961952</v>
       </c>
       <c r="C54">
-        <v>1.756255437475329E-12</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -4512,7 +4512,7 @@
         <v>-0.00021</v>
       </c>
       <c r="F54">
-        <v>-9.220341046745479E-20</v>
+        <v>-0</v>
       </c>
       <c r="G54">
         <v>20</v>
@@ -4555,7 +4555,7 @@
         <v>21.81522212386757</v>
       </c>
       <c r="C56">
-        <v>1.141566034358964E-11</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -4564,7 +4564,7 @@
         <v>-0.00023</v>
       </c>
       <c r="F56">
-        <v>-6.564004697564044E-19</v>
+        <v>-0</v>
       </c>
       <c r="G56">
         <v>20</v>
@@ -4633,7 +4633,7 @@
         <v>21.72073034738524</v>
       </c>
       <c r="C59">
-        <v>2.634383156212994E-12</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -4642,7 +4642,7 @@
         <v>-0.00169</v>
       </c>
       <c r="F59">
-        <v>-1.11302688349999E-18</v>
+        <v>-0</v>
       </c>
       <c r="G59">
         <v>20</v>
@@ -4711,7 +4711,7 @@
         <v>23.27326995192937</v>
       </c>
       <c r="C62">
-        <v>1.931880981222862E-11</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>-0.00168</v>
       </c>
       <c r="F62">
-        <v>-8.113900121136021E-18</v>
+        <v>-0</v>
       </c>
       <c r="G62">
         <v>20</v>
@@ -4815,7 +4815,7 @@
         <v>24</v>
       </c>
       <c r="C66">
-        <v>4.390638593688324E-12</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4824,7 +4824,7 @@
         <v>-0.00074</v>
       </c>
       <c r="F66">
-        <v>-8.122681398323399E-19</v>
+        <v>-0</v>
       </c>
       <c r="G66">
         <v>20</v>
@@ -4945,7 +4945,7 @@
         <v>23.50357588407085</v>
       </c>
       <c r="C71">
-        <v>5.268766312425988E-12</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>-1E-05</v>
       </c>
       <c r="F71">
-        <v>-1.317191578106497E-20</v>
+        <v>-0</v>
       </c>
       <c r="G71">
         <v>20</v>
@@ -5049,7 +5049,7 @@
         <v>24</v>
       </c>
       <c r="C75">
-        <v>637.920648217693</v>
+        <v>637.9206482176929</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -5058,7 +5058,7 @@
         <v>-0.00055</v>
       </c>
       <c r="F75">
-        <v>-8.77140891299328E-05</v>
+        <v>-8.771408912993278E-05</v>
       </c>
       <c r="G75">
         <v>20</v>
@@ -5960,7 +5960,7 @@
         <v>0.08723</v>
       </c>
       <c r="F12">
-        <v>0.003158128625069064</v>
+        <v>0.003158128625069065</v>
       </c>
       <c r="G12">
         <v>20</v>
@@ -11274,7 +11274,7 @@
         <v>0.120495</v>
       </c>
       <c r="F21">
-        <v>0.001364919329795428</v>
+        <v>0.001364919329795429</v>
       </c>
       <c r="G21">
         <v>20</v>
@@ -11690,7 +11690,7 @@
         <v>0.219605</v>
       </c>
       <c r="F37">
-        <v>0.007950714624650829</v>
+        <v>0.00795071462465083</v>
       </c>
       <c r="G37">
         <v>20</v>
@@ -13389,7 +13389,7 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>1520.872738260144</v>
+        <v>1520.872738260143</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -13398,7 +13398,7 @@
         <v>0.127255</v>
       </c>
       <c r="F5">
-        <v>0.04838466507682365</v>
+        <v>0.04838466507682364</v>
       </c>
       <c r="G5">
         <v>20</v>
@@ -14013,7 +14013,7 @@
         <v>20</v>
       </c>
       <c r="C29">
-        <v>1520.872738260144</v>
+        <v>1520.872738260143</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -14022,7 +14022,7 @@
         <v>0.1742825</v>
       </c>
       <c r="F29">
-        <v>0.06626537575145586</v>
+        <v>0.06626537575145584</v>
       </c>
       <c r="G29">
         <v>20</v>
@@ -14169,7 +14169,7 @@
         <v>20</v>
       </c>
       <c r="C35">
-        <v>1520.872738260144</v>
+        <v>1520.872738260143</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -14178,7 +14178,7 @@
         <v>0.19982</v>
       </c>
       <c r="F35">
-        <v>0.07597519763978548</v>
+        <v>0.07597519763978547</v>
       </c>
       <c r="G35">
         <v>20</v>
@@ -14871,7 +14871,7 @@
         <v>20</v>
       </c>
       <c r="C62">
-        <v>980.6861424777024</v>
+        <v>980.6861424777023</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -14880,7 +14880,7 @@
         <v>0.12247</v>
       </c>
       <c r="F62">
-        <v>0.03002615796731106</v>
+        <v>0.03002615796731105</v>
       </c>
       <c r="G62">
         <v>20</v>
@@ -20324,7 +20324,7 @@
         <v>0.102115</v>
       </c>
       <c r="F76">
-        <v>0.00313517620984855</v>
+        <v>0.003135176209848549</v>
       </c>
       <c r="G76">
         <v>20</v>
@@ -22338,13 +22338,13 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>2.189433722321791E-12</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>-1.5E-05</v>
       </c>
       <c r="F56">
-        <v>-8.210376458706718E-21</v>
+        <v>-0</v>
       </c>
       <c r="G56">
         <v>20</v>
@@ -23786,7 +23786,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>91.61950841930637</v>
+        <v>91.61950841930638</v>
       </c>
       <c r="E14">
         <v>0.06074</v>
@@ -23838,7 +23838,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>85.94857816303123</v>
+        <v>85.94857816303124</v>
       </c>
       <c r="E16">
         <v>0.055195</v>
@@ -24072,13 +24072,13 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>91.61950841930637</v>
+        <v>91.61950841930638</v>
       </c>
       <c r="E25">
         <v>0.029515</v>
       </c>
       <c r="F25">
-        <v>0.0006760374477489569</v>
+        <v>0.000676037447748957</v>
       </c>
       <c r="G25">
         <v>20</v>
@@ -24098,13 +24098,13 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>85.94857816303123</v>
+        <v>85.94857816303124</v>
       </c>
       <c r="E26">
         <v>0.0258</v>
       </c>
       <c r="F26">
-        <v>0.0005543683291515515</v>
+        <v>0.0005543683291515516</v>
       </c>
       <c r="G26">
         <v>20</v>
@@ -24416,7 +24416,7 @@
         <v>-0.0005</v>
       </c>
       <c r="F38">
-        <v>-2.562976419309851E-05</v>
+        <v>-2.56297641930985E-05</v>
       </c>
       <c r="G38">
         <v>20</v>
@@ -26976,13 +26976,13 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>311.3680558499258</v>
+        <v>311.3680558499259</v>
       </c>
       <c r="E39">
         <v>0.0933875</v>
       </c>
       <c r="F39">
-        <v>0.007269471078921237</v>
+        <v>0.007269471078921239</v>
       </c>
       <c r="G39">
         <v>20</v>
@@ -29620,7 +29620,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>375.1660212330084</v>
+        <v>375.1660212330083</v>
       </c>
       <c r="E43">
         <v>-0.0035575</v>
